--- a/data/nzd0035/nzd0035.xlsx
+++ b/data/nzd0035/nzd0035.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F527"/>
+  <dimension ref="A1:F528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13080,6 +13080,30 @@
       <c r="F527" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>352.37</v>
+      </c>
+      <c r="C528" t="n">
+        <v>372.57</v>
+      </c>
+      <c r="D528" t="n">
+        <v>372.06</v>
+      </c>
+      <c r="E528" t="n">
+        <v>385.52</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B589"/>
+  <dimension ref="A1:B590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18987,6 +19011,16 @@
       </c>
       <c r="B589" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -19155,28 +19189,28 @@
         <v>0.0611</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06074339642003614</v>
+        <v>0.05712257663519957</v>
       </c>
       <c r="J2" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K2" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01285247613339691</v>
+        <v>0.01129780928062896</v>
       </c>
       <c r="M2" t="n">
-        <v>3.271849435158305</v>
+        <v>3.28504437331416</v>
       </c>
       <c r="N2" t="n">
-        <v>16.67543757223905</v>
+        <v>16.83731877673477</v>
       </c>
       <c r="O2" t="n">
-        <v>4.083556975510327</v>
+        <v>4.103330205666461</v>
       </c>
       <c r="P2" t="n">
-        <v>360.8877266230288</v>
+        <v>360.9236479478781</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19233,28 +19267,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1048327238394472</v>
+        <v>0.1023531818931436</v>
       </c>
       <c r="J3" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K3" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03127764541195721</v>
+        <v>0.02984225463927781</v>
       </c>
       <c r="M3" t="n">
-        <v>3.614118277921853</v>
+        <v>3.620163774742866</v>
       </c>
       <c r="N3" t="n">
-        <v>20.24949445506301</v>
+        <v>20.30328872151831</v>
       </c>
       <c r="O3" t="n">
-        <v>4.499943827989746</v>
+        <v>4.505917078855125</v>
       </c>
       <c r="P3" t="n">
-        <v>376.7991178452628</v>
+        <v>376.8234972050744</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19311,28 +19345,28 @@
         <v>0.0502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09866835695889856</v>
+        <v>0.09507738520050267</v>
       </c>
       <c r="J4" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K4" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02421289803074123</v>
+        <v>0.0224270122851804</v>
       </c>
       <c r="M4" t="n">
-        <v>3.853534378995634</v>
+        <v>3.863216319032679</v>
       </c>
       <c r="N4" t="n">
-        <v>23.34098974934389</v>
+        <v>23.49011813241354</v>
       </c>
       <c r="O4" t="n">
-        <v>4.831251364744324</v>
+        <v>4.846660513427111</v>
       </c>
       <c r="P4" t="n">
-        <v>379.5893866387947</v>
+        <v>379.6246938021607</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19389,28 +19423,28 @@
         <v>0.0301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2882417407376932</v>
+        <v>0.2837659967251678</v>
       </c>
       <c r="J5" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K5" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08250528036068416</v>
+        <v>0.08005653997643158</v>
       </c>
       <c r="M5" t="n">
-        <v>5.509603624181972</v>
+        <v>5.524935440437957</v>
       </c>
       <c r="N5" t="n">
-        <v>54.9655715032519</v>
+        <v>55.1617451431679</v>
       </c>
       <c r="O5" t="n">
-        <v>7.413876954957636</v>
+        <v>7.427095336884259</v>
       </c>
       <c r="P5" t="n">
-        <v>390.5507383811217</v>
+        <v>390.5947448049164</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19448,7 +19482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F527"/>
+  <dimension ref="A1:F528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36307,6 +36341,38 @@
         </is>
       </c>
     </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-34.95050856768205,173.61969615205268</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-34.951222041838435,173.6198215413718</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-34.95187823669017,173.62013071266085</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-34.952340693228635,173.6208084311577</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0035/nzd0035.xlsx
+++ b/data/nzd0035/nzd0035.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F528"/>
+  <dimension ref="A1:F530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13104,6 +13104,54 @@
       <c r="F528" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>352.67</v>
+      </c>
+      <c r="C529" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="D529" t="n">
+        <v>372.01</v>
+      </c>
+      <c r="E529" t="n">
+        <v>382.92</v>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>353.39</v>
+      </c>
+      <c r="C530" t="n">
+        <v>371.86</v>
+      </c>
+      <c r="D530" t="n">
+        <v>371.21</v>
+      </c>
+      <c r="E530" t="n">
+        <v>380.66</v>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B590"/>
+  <dimension ref="A1:B592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19021,6 +19069,26 @@
       </c>
       <c r="B590" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -19189,28 +19257,28 @@
         <v>0.0611</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05712257663519957</v>
+        <v>0.05043709980900619</v>
       </c>
       <c r="J2" t="n">
+        <v>529</v>
+      </c>
+      <c r="K2" t="n">
         <v>527</v>
       </c>
-      <c r="K2" t="n">
-        <v>525</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01129780928062896</v>
+        <v>0.00872871176964185</v>
       </c>
       <c r="M2" t="n">
-        <v>3.28504437331416</v>
+        <v>3.308471586060703</v>
       </c>
       <c r="N2" t="n">
-        <v>16.83731877673477</v>
+        <v>17.10533643395149</v>
       </c>
       <c r="O2" t="n">
-        <v>4.103330205666461</v>
+        <v>4.135859817976365</v>
       </c>
       <c r="P2" t="n">
-        <v>360.9236479478781</v>
+        <v>360.9901465286588</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19267,28 +19335,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1023531818931436</v>
+        <v>0.09696897104310487</v>
       </c>
       <c r="J3" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K3" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02984225463927781</v>
+        <v>0.02679380065687487</v>
       </c>
       <c r="M3" t="n">
-        <v>3.620163774742866</v>
+        <v>3.634253183995159</v>
       </c>
       <c r="N3" t="n">
-        <v>20.30328872151831</v>
+        <v>20.44481013836333</v>
       </c>
       <c r="O3" t="n">
-        <v>4.505917078855125</v>
+        <v>4.521593760872745</v>
       </c>
       <c r="P3" t="n">
-        <v>376.8234972050744</v>
+        <v>376.8765768465959</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19345,28 +19413,28 @@
         <v>0.0502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09507738520050267</v>
+        <v>0.08766216492144951</v>
       </c>
       <c r="J4" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K4" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0224270122851804</v>
+        <v>0.01894940925295252</v>
       </c>
       <c r="M4" t="n">
-        <v>3.863216319032679</v>
+        <v>3.884145824265712</v>
       </c>
       <c r="N4" t="n">
-        <v>23.49011813241354</v>
+        <v>23.81590418902296</v>
       </c>
       <c r="O4" t="n">
-        <v>4.846660513427111</v>
+        <v>4.880154115294205</v>
       </c>
       <c r="P4" t="n">
-        <v>379.6246938021607</v>
+        <v>379.6977972815802</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19423,28 +19491,28 @@
         <v>0.0301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2837659967251678</v>
+        <v>0.2722879420086066</v>
       </c>
       <c r="J5" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K5" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08005653997643158</v>
+        <v>0.0734941405682914</v>
       </c>
       <c r="M5" t="n">
-        <v>5.524935440437957</v>
+        <v>5.570793098976979</v>
       </c>
       <c r="N5" t="n">
-        <v>55.1617451431679</v>
+        <v>55.94988987422646</v>
       </c>
       <c r="O5" t="n">
-        <v>7.427095336884259</v>
+        <v>7.479965900605862</v>
       </c>
       <c r="P5" t="n">
-        <v>390.5947448049164</v>
+        <v>390.7079039242899</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19482,7 +19550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F528"/>
+  <dimension ref="A1:F530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36373,6 +36441,70 @@
         </is>
       </c>
     </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-34.95050884603292,173.61969942011822</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-34.95122287991848,173.61981427462484</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>-34.95187846908061,173.62013024341437</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-34.95235596025395,173.6207868211939</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>-34.950509514074675,173.61970726347562</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>-34.9512229299531,173.61981384078922</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>-34.95188218732754,173.62012273547026</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>-34.95236923081902,173.62076803714191</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0035/nzd0035.xlsx
+++ b/data/nzd0035/nzd0035.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F530"/>
+  <dimension ref="A1:F534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13152,6 +13152,102 @@
       <c r="F530" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>353.21</v>
+      </c>
+      <c r="C531" t="n">
+        <v>370.46</v>
+      </c>
+      <c r="D531" t="n">
+        <v>370.1</v>
+      </c>
+      <c r="E531" t="n">
+        <v>373.35</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>354.01</v>
+      </c>
+      <c r="C532" t="n">
+        <v>370.82</v>
+      </c>
+      <c r="D532" t="n">
+        <v>370.34</v>
+      </c>
+      <c r="E532" t="n">
+        <v>375.64</v>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>354.45</v>
+      </c>
+      <c r="C533" t="n">
+        <v>371</v>
+      </c>
+      <c r="D533" t="n">
+        <v>370.87</v>
+      </c>
+      <c r="E533" t="n">
+        <v>377.02</v>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>355.64</v>
+      </c>
+      <c r="C534" t="n">
+        <v>371.85</v>
+      </c>
+      <c r="D534" t="n">
+        <v>371.39</v>
+      </c>
+      <c r="E534" t="n">
+        <v>376.88</v>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B592"/>
+  <dimension ref="A1:B596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19089,6 +19185,46 @@
       </c>
       <c r="B592" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -19257,28 +19393,28 @@
         <v>0.0611</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05043709980900619</v>
+        <v>0.0392509572608955</v>
       </c>
       <c r="J2" t="n">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="K2" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00872871176964185</v>
+        <v>0.005241918774333998</v>
       </c>
       <c r="M2" t="n">
-        <v>3.308471586060703</v>
+        <v>3.343850305394376</v>
       </c>
       <c r="N2" t="n">
-        <v>17.10533643395149</v>
+        <v>17.45308244735574</v>
       </c>
       <c r="O2" t="n">
-        <v>4.135859817976365</v>
+        <v>4.177688648924875</v>
       </c>
       <c r="P2" t="n">
-        <v>360.9901465286588</v>
+        <v>361.1017948356276</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19335,28 +19471,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09696897104310487</v>
+        <v>0.08532111035349339</v>
       </c>
       <c r="J3" t="n">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="K3" t="n">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02679380065687487</v>
+        <v>0.02067380723982537</v>
       </c>
       <c r="M3" t="n">
-        <v>3.634253183995159</v>
+        <v>3.666578676641353</v>
       </c>
       <c r="N3" t="n">
-        <v>20.44481013836333</v>
+        <v>20.81156507267249</v>
       </c>
       <c r="O3" t="n">
-        <v>4.521593760872745</v>
+        <v>4.561969429168996</v>
       </c>
       <c r="P3" t="n">
-        <v>376.8765768465959</v>
+        <v>376.9918073879171</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19413,28 +19549,28 @@
         <v>0.0502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08766216492144951</v>
+        <v>0.07195100086797027</v>
       </c>
       <c r="J4" t="n">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="K4" t="n">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01894940925295252</v>
+        <v>0.0125504338812843</v>
       </c>
       <c r="M4" t="n">
-        <v>3.884145824265712</v>
+        <v>3.931809232058247</v>
       </c>
       <c r="N4" t="n">
-        <v>23.81590418902296</v>
+        <v>24.58185761388909</v>
       </c>
       <c r="O4" t="n">
-        <v>4.880154115294205</v>
+        <v>4.958009440681723</v>
       </c>
       <c r="P4" t="n">
-        <v>379.6977972815802</v>
+        <v>379.8532275427573</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19491,28 +19627,28 @@
         <v>0.0301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2722879420086066</v>
+        <v>0.2415467181027603</v>
       </c>
       <c r="J5" t="n">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="K5" t="n">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0734941405682914</v>
+        <v>0.05617963659218672</v>
       </c>
       <c r="M5" t="n">
-        <v>5.570793098976979</v>
+        <v>5.716499161910465</v>
       </c>
       <c r="N5" t="n">
-        <v>55.94988987422646</v>
+        <v>59.15582783798751</v>
       </c>
       <c r="O5" t="n">
-        <v>7.479965900605862</v>
+        <v>7.691282587318419</v>
       </c>
       <c r="P5" t="n">
-        <v>390.7079039242899</v>
+        <v>391.0120241560206</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19550,7 +19686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F530"/>
+  <dimension ref="A1:F534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36505,6 +36641,134 @@
         </is>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>-34.95050934706428,173.61970530263625</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>-34.951224681163666,173.6197986565413</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>-34.95188734639439,173.62011231819668</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-34.95241215461824,173.6207072798349</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>-34.95051008933244,173.61971401747792</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>-34.95122423085254,173.61980256106224</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>-34.95188623092056,173.62011457058028</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-34.952398707904614,173.62072631325253</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>-34.950510497579664,173.6197188106409</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>-34.95122400569695,173.6198045133227</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>-34.951883767582345,173.62011954459382</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>-34.95239060464345,173.62073778316932</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>-34.95051160170189,173.61973177396825</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>-34.951222942461754,173.61981373233027</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>-34.95188135072203,173.62012442475773</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-34.95239142671348,173.6207366195547</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0035/nzd0035.xlsx
+++ b/data/nzd0035/nzd0035.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F534"/>
+  <dimension ref="A1:F536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13248,6 +13248,54 @@
       <c r="F534" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>355.84</v>
+      </c>
+      <c r="C535" t="n">
+        <v>371.5</v>
+      </c>
+      <c r="D535" t="n">
+        <v>371.28</v>
+      </c>
+      <c r="E535" t="n">
+        <v>378.11</v>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="C536" t="n">
+        <v>371.06</v>
+      </c>
+      <c r="D536" t="n">
+        <v>370.78</v>
+      </c>
+      <c r="E536" t="n">
+        <v>379.77</v>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13262,7 +13310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B596"/>
+  <dimension ref="A1:B598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19225,6 +19273,26 @@
       </c>
       <c r="B596" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -19393,28 +19461,28 @@
         <v>0.0611</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0392509572608955</v>
+        <v>0.03499516800242271</v>
       </c>
       <c r="J2" t="n">
+        <v>535</v>
+      </c>
+      <c r="K2" t="n">
         <v>533</v>
       </c>
-      <c r="K2" t="n">
-        <v>531</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.005241918774333998</v>
+        <v>0.004170740047161559</v>
       </c>
       <c r="M2" t="n">
-        <v>3.343850305394376</v>
+        <v>3.354622305294358</v>
       </c>
       <c r="N2" t="n">
-        <v>17.45308244735574</v>
+        <v>17.52628062905616</v>
       </c>
       <c r="O2" t="n">
-        <v>4.177688648924875</v>
+        <v>4.18644009022656</v>
       </c>
       <c r="P2" t="n">
-        <v>361.1017948356276</v>
+        <v>361.1444380262346</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19471,28 +19539,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08532111035349339</v>
+        <v>0.07981830878736051</v>
       </c>
       <c r="J3" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="K3" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02067380723982537</v>
+        <v>0.01807742033756865</v>
       </c>
       <c r="M3" t="n">
-        <v>3.666578676641353</v>
+        <v>3.680831355865019</v>
       </c>
       <c r="N3" t="n">
-        <v>20.81156507267249</v>
+        <v>20.96908196107797</v>
       </c>
       <c r="O3" t="n">
-        <v>4.561969429168996</v>
+        <v>4.579201017762593</v>
       </c>
       <c r="P3" t="n">
-        <v>376.9918073879171</v>
+        <v>377.0464637869728</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19549,28 +19617,28 @@
         <v>0.0502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07195100086797027</v>
+        <v>0.0645479917512408</v>
       </c>
       <c r="J4" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="K4" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0125504338812843</v>
+        <v>0.01003104412867095</v>
       </c>
       <c r="M4" t="n">
-        <v>3.931809232058247</v>
+        <v>3.955153584394054</v>
       </c>
       <c r="N4" t="n">
-        <v>24.58185761388909</v>
+        <v>24.91578003446782</v>
       </c>
       <c r="O4" t="n">
-        <v>4.958009440681723</v>
+        <v>4.991570898471524</v>
       </c>
       <c r="P4" t="n">
-        <v>379.8532275427573</v>
+        <v>379.9267572278205</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19627,28 +19695,28 @@
         <v>0.0301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2415467181027603</v>
+        <v>0.2288000867415461</v>
       </c>
       <c r="J5" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="K5" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05617963659218672</v>
+        <v>0.05005552985699435</v>
       </c>
       <c r="M5" t="n">
-        <v>5.716499161910465</v>
+        <v>5.776185970539789</v>
       </c>
       <c r="N5" t="n">
-        <v>59.15582783798751</v>
+        <v>60.19939256736875</v>
       </c>
       <c r="O5" t="n">
-        <v>7.691282587318419</v>
+        <v>7.758826751988264</v>
       </c>
       <c r="P5" t="n">
-        <v>391.0120241560206</v>
+        <v>391.1386149950941</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19686,7 +19754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F534"/>
+  <dimension ref="A1:F536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36769,6 +36837,70 @@
         </is>
       </c>
     </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>-34.950511787268496,173.61973395267879</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>-34.95122338026456,173.61980993626838</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>-34.95188186198095,173.62012339241537</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>-34.95238420424077,173.6207468427397</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>-34.95051213984498,173.61973809222874</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>-34.95122393064507,173.61980516407618</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>-34.95188418588507,173.62011869995</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-34.95237445683723,173.62076063988084</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0035/nzd0035.xlsx
+++ b/data/nzd0035/nzd0035.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F536"/>
+  <dimension ref="A1:F537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13296,6 +13296,30 @@
       <c r="F536" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>357.55</v>
+      </c>
+      <c r="C537" t="n">
+        <v>371.52</v>
+      </c>
+      <c r="D537" t="n">
+        <v>371.96</v>
+      </c>
+      <c r="E537" t="n">
+        <v>379.89</v>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13310,7 +13334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B598"/>
+  <dimension ref="A1:B599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19293,6 +19317,16 @@
       </c>
       <c r="B598" t="n">
         <v>0.22</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -19461,28 +19495,28 @@
         <v>0.0611</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03499516800242271</v>
+        <v>0.03342146848598889</v>
       </c>
       <c r="J2" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K2" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004170740047161559</v>
+        <v>0.00381199077359784</v>
       </c>
       <c r="M2" t="n">
-        <v>3.354622305294358</v>
+        <v>3.357013848983655</v>
       </c>
       <c r="N2" t="n">
-        <v>17.52628062905616</v>
+        <v>17.53155835084644</v>
       </c>
       <c r="O2" t="n">
-        <v>4.18644009022656</v>
+        <v>4.18707037806226</v>
       </c>
       <c r="P2" t="n">
-        <v>361.1444380262346</v>
+        <v>361.1602488703604</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19539,28 +19573,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07981830878736051</v>
+        <v>0.07718208357582872</v>
       </c>
       <c r="J3" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K3" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01807742033756865</v>
+        <v>0.0169013877524492</v>
       </c>
       <c r="M3" t="n">
-        <v>3.680831355865019</v>
+        <v>3.68734398594391</v>
       </c>
       <c r="N3" t="n">
-        <v>20.96908196107797</v>
+        <v>21.03851716348675</v>
       </c>
       <c r="O3" t="n">
-        <v>4.579201017762593</v>
+        <v>4.586776336762754</v>
       </c>
       <c r="P3" t="n">
-        <v>377.0464637869728</v>
+        <v>377.0727164665759</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19617,28 +19651,28 @@
         <v>0.0502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0645479917512408</v>
+        <v>0.06121073351904012</v>
       </c>
       <c r="J4" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K4" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01003104412867095</v>
+        <v>0.009002111286671943</v>
       </c>
       <c r="M4" t="n">
-        <v>3.955153584394054</v>
+        <v>3.965075637753267</v>
       </c>
       <c r="N4" t="n">
-        <v>24.91578003446782</v>
+        <v>25.04326399747089</v>
       </c>
       <c r="O4" t="n">
-        <v>4.991570898471524</v>
+        <v>5.004324529591471</v>
       </c>
       <c r="P4" t="n">
-        <v>379.9267572278205</v>
+        <v>379.9599910997749</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19695,28 +19729,28 @@
         <v>0.0301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2288000867415461</v>
+        <v>0.2228269739457031</v>
       </c>
       <c r="J5" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K5" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05005552985699435</v>
+        <v>0.04735682743752612</v>
       </c>
       <c r="M5" t="n">
-        <v>5.776185970539789</v>
+        <v>5.803427459222013</v>
       </c>
       <c r="N5" t="n">
-        <v>60.19939256736875</v>
+        <v>60.64438501506758</v>
       </c>
       <c r="O5" t="n">
-        <v>7.758826751988264</v>
+        <v>7.78745048235092</v>
       </c>
       <c r="P5" t="n">
-        <v>391.1386149950941</v>
+        <v>391.1980978555785</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19754,7 +19788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F536"/>
+  <dimension ref="A1:F537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36901,6 +36935,38 @@
         </is>
       </c>
     </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>-34.950513373861526,173.61975258065402</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>-34.951223355247265,173.6198101531862</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>-34.95187870147106,173.62012977416785</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>-34.95237375220558,173.6207616372644</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0035/nzd0035.xlsx
+++ b/data/nzd0035/nzd0035.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F537"/>
+  <dimension ref="A1:F541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13320,6 +13320,102 @@
       <c r="F537" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>358.24</v>
+      </c>
+      <c r="C538" t="n">
+        <v>371.73</v>
+      </c>
+      <c r="D538" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="E538" t="n">
+        <v>381.42</v>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="C539" t="n">
+        <v>372.32</v>
+      </c>
+      <c r="D539" t="n">
+        <v>372.11</v>
+      </c>
+      <c r="E539" t="n">
+        <v>383.67</v>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>360.09</v>
+      </c>
+      <c r="C540" t="n">
+        <v>372.09</v>
+      </c>
+      <c r="D540" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="E540" t="n">
+        <v>384.06</v>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>359.65</v>
+      </c>
+      <c r="C541" t="n">
+        <v>371.66</v>
+      </c>
+      <c r="D541" t="n">
+        <v>371.48</v>
+      </c>
+      <c r="E541" t="n">
+        <v>386.02</v>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B599"/>
+  <dimension ref="A1:B603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19327,6 +19423,46 @@
       </c>
       <c r="B599" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -19495,28 +19631,28 @@
         <v>0.0611</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03342146848598889</v>
+        <v>0.02950189039294895</v>
       </c>
       <c r="J2" t="n">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="K2" t="n">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00381199077359784</v>
+        <v>0.003008511748636589</v>
       </c>
       <c r="M2" t="n">
-        <v>3.357013848983655</v>
+        <v>3.353318748250977</v>
       </c>
       <c r="N2" t="n">
-        <v>17.53155835084644</v>
+        <v>17.46433050219044</v>
       </c>
       <c r="O2" t="n">
-        <v>4.18707037806226</v>
+        <v>4.179034637591609</v>
       </c>
       <c r="P2" t="n">
-        <v>361.1602488703604</v>
+        <v>361.199821263874</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19573,28 +19709,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07718208357582872</v>
+        <v>0.06741155210023396</v>
       </c>
       <c r="J3" t="n">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="K3" t="n">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0169013877524492</v>
+        <v>0.01291669338524704</v>
       </c>
       <c r="M3" t="n">
-        <v>3.68734398594391</v>
+        <v>3.709468785111008</v>
       </c>
       <c r="N3" t="n">
-        <v>21.03851716348675</v>
+        <v>21.25658128993414</v>
       </c>
       <c r="O3" t="n">
-        <v>4.586776336762754</v>
+        <v>4.610486014503692</v>
       </c>
       <c r="P3" t="n">
-        <v>377.0727164665759</v>
+        <v>377.1705349420268</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19651,28 +19787,28 @@
         <v>0.0502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06121073351904012</v>
+        <v>0.04788442498504968</v>
       </c>
       <c r="J4" t="n">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="K4" t="n">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009002111286671943</v>
+        <v>0.005462551782770886</v>
       </c>
       <c r="M4" t="n">
-        <v>3.965075637753267</v>
+        <v>4.005740385881331</v>
       </c>
       <c r="N4" t="n">
-        <v>25.04326399747089</v>
+        <v>25.55267874770888</v>
       </c>
       <c r="O4" t="n">
-        <v>5.004324529591471</v>
+        <v>5.05496575138832</v>
       </c>
       <c r="P4" t="n">
-        <v>379.9599910997749</v>
+        <v>380.0934101020919</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19729,28 +19865,28 @@
         <v>0.0301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2228269739457031</v>
+        <v>0.2046664799353831</v>
       </c>
       <c r="J5" t="n">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="K5" t="n">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04735682743752612</v>
+        <v>0.04001877938910814</v>
       </c>
       <c r="M5" t="n">
-        <v>5.803427459222013</v>
+        <v>5.874643636842267</v>
       </c>
       <c r="N5" t="n">
-        <v>60.64438501506758</v>
+        <v>61.50559832321993</v>
       </c>
       <c r="O5" t="n">
-        <v>7.78745048235092</v>
+        <v>7.842550498608213</v>
       </c>
       <c r="P5" t="n">
-        <v>391.1980978555785</v>
+        <v>391.3798771016051</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19788,7 +19924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F537"/>
+  <dimension ref="A1:F541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36967,6 +37103,134 @@
         </is>
       </c>
     </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>-34.95051401406492,173.61976009720564</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>-34.95122309256559,173.61981243082334</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>-34.95187944512048,173.6201282725791</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>-34.95236476815145,173.6207743539034</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>-34.95051453364993,173.61976619759542</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>-34.95122235455493,173.6198188298991</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>-34.95187800429972,173.6201311819073</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>-34.952351556304734,173.62079305483812</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>-34.95051573054997,173.61978025027932</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>-34.95122264225404,173.61981633534415</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>-34.95187944512048,173.6201282725791</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>-34.95234926625101,173.62079629633286</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>-34.95051532230517,173.6197754571158</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>-34.95122318012615,173.61981167161096</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>-34.95188093241926,173.62012526940146</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-34.9523377572618,173.62081258691904</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0035/nzd0035.xlsx
+++ b/data/nzd0035/nzd0035.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F541"/>
+  <dimension ref="A1:F543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13414,6 +13414,54 @@
         <v>386.02</v>
       </c>
       <c r="F541" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>359.82</v>
+      </c>
+      <c r="C542" t="n">
+        <v>371.82</v>
+      </c>
+      <c r="D542" t="n">
+        <v>371.39</v>
+      </c>
+      <c r="E542" t="n">
+        <v>385.03</v>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>359.58</v>
+      </c>
+      <c r="C543" t="n">
+        <v>372.35</v>
+      </c>
+      <c r="D543" t="n">
+        <v>371.94</v>
+      </c>
+      <c r="E543" t="n">
+        <v>386.91</v>
+      </c>
+      <c r="F543" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13430,7 +13478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B603"/>
+  <dimension ref="A1:B605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19463,6 +19511,26 @@
       </c>
       <c r="B603" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -19631,28 +19699,28 @@
         <v>0.0611</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02950189039294895</v>
+        <v>0.02793780755830502</v>
       </c>
       <c r="J2" t="n">
+        <v>542</v>
+      </c>
+      <c r="K2" t="n">
         <v>540</v>
       </c>
-      <c r="K2" t="n">
-        <v>538</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.003008511748636589</v>
+        <v>0.002716736301151101</v>
       </c>
       <c r="M2" t="n">
-        <v>3.353318748250977</v>
+        <v>3.349314162881965</v>
       </c>
       <c r="N2" t="n">
-        <v>17.46433050219044</v>
+        <v>17.41883359143898</v>
       </c>
       <c r="O2" t="n">
-        <v>4.179034637591609</v>
+        <v>4.173587616360651</v>
       </c>
       <c r="P2" t="n">
-        <v>361.199821263874</v>
+        <v>361.2156850776685</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19709,28 +19777,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06741155210023396</v>
+        <v>0.06274218570483063</v>
       </c>
       <c r="J3" t="n">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="K3" t="n">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01291669338524704</v>
+        <v>0.01120367314559245</v>
       </c>
       <c r="M3" t="n">
-        <v>3.709468785111008</v>
+        <v>3.719241189740607</v>
       </c>
       <c r="N3" t="n">
-        <v>21.25658128993414</v>
+        <v>21.35158667063094</v>
       </c>
       <c r="O3" t="n">
-        <v>4.610486014503692</v>
+        <v>4.620777712748248</v>
       </c>
       <c r="P3" t="n">
-        <v>377.1705349420268</v>
+        <v>377.2174766197738</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19787,28 +19855,28 @@
         <v>0.0502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04788442498504968</v>
+        <v>0.0413014569878038</v>
       </c>
       <c r="J4" t="n">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="K4" t="n">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005462551782770886</v>
+        <v>0.004046375514649481</v>
       </c>
       <c r="M4" t="n">
-        <v>4.005740385881331</v>
+        <v>4.025841475653881</v>
       </c>
       <c r="N4" t="n">
-        <v>25.55267874770888</v>
+        <v>25.80287682892925</v>
       </c>
       <c r="O4" t="n">
-        <v>5.05496575138832</v>
+        <v>5.079653219357524</v>
       </c>
       <c r="P4" t="n">
-        <v>380.0934101020919</v>
+        <v>380.1595901778207</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19865,28 +19933,28 @@
         <v>0.0301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2046664799353831</v>
+        <v>0.1972862593068522</v>
       </c>
       <c r="J5" t="n">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="K5" t="n">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04001877938910814</v>
+        <v>0.03731260618119636</v>
       </c>
       <c r="M5" t="n">
-        <v>5.874643636842267</v>
+        <v>5.899086042088991</v>
       </c>
       <c r="N5" t="n">
-        <v>61.50559832321993</v>
+        <v>61.7145872918078</v>
       </c>
       <c r="O5" t="n">
-        <v>7.842550498608213</v>
+        <v>7.855863242942038</v>
       </c>
       <c r="P5" t="n">
-        <v>391.3798771016051</v>
+        <v>391.4540673765654</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19924,7 +19992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F541"/>
+  <dimension ref="A1:F543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37231,6 +37299,70 @@
         </is>
       </c>
     </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>-34.95051548003613,173.6197773090199</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>-34.951222979987705,173.61981340695357</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>-34.95188135072203,173.62012442475773</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-34.95234357047601,173.62080435851126</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>-34.95051525735711,173.61977469456704</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>-34.95122231702895,173.61981915527582</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>-34.951878794427245,173.6201295864693</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-34.95233253124048,173.62081998417352</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0035/nzd0035.xlsx
+++ b/data/nzd0035/nzd0035.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F543"/>
+  <dimension ref="A1:F547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13462,6 +13462,102 @@
         <v>386.91</v>
       </c>
       <c r="F543" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>360.43</v>
+      </c>
+      <c r="C544" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="D544" t="n">
+        <v>373</v>
+      </c>
+      <c r="E544" t="n">
+        <v>386.76</v>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>360.43</v>
+      </c>
+      <c r="C545" t="n">
+        <v>374.67</v>
+      </c>
+      <c r="D545" t="n">
+        <v>373.57</v>
+      </c>
+      <c r="E545" t="n">
+        <v>385.97</v>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>359.89</v>
+      </c>
+      <c r="C546" t="n">
+        <v>374.52</v>
+      </c>
+      <c r="D546" t="n">
+        <v>374.42</v>
+      </c>
+      <c r="E546" t="n">
+        <v>388.58</v>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>359.89</v>
+      </c>
+      <c r="C547" t="n">
+        <v>374.71</v>
+      </c>
+      <c r="D547" t="n">
+        <v>374.92</v>
+      </c>
+      <c r="E547" t="n">
+        <v>389.71</v>
+      </c>
+      <c r="F547" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13478,7 +13574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B605"/>
+  <dimension ref="A1:B609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19531,6 +19627,46 @@
       </c>
       <c r="B605" t="n">
         <v>0.09</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -19699,28 +19835,28 @@
         <v>0.0611</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02793780755830502</v>
+        <v>0.02549737861811585</v>
       </c>
       <c r="J2" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K2" t="n">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002716736301151101</v>
+        <v>0.00229574583669212</v>
       </c>
       <c r="M2" t="n">
-        <v>3.349314162881965</v>
+        <v>3.337622771034862</v>
       </c>
       <c r="N2" t="n">
-        <v>17.41883359143898</v>
+        <v>17.31478762110507</v>
       </c>
       <c r="O2" t="n">
-        <v>4.173587616360651</v>
+        <v>4.161104134854723</v>
       </c>
       <c r="P2" t="n">
-        <v>361.2156850776685</v>
+        <v>361.2405526931046</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19777,28 +19913,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06274218570483063</v>
+        <v>0.05675804286316099</v>
       </c>
       <c r="J3" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K3" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01120367314559245</v>
+        <v>0.009265218486312676</v>
       </c>
       <c r="M3" t="n">
-        <v>3.719241189740607</v>
+        <v>3.72197915596848</v>
       </c>
       <c r="N3" t="n">
-        <v>21.35158667063094</v>
+        <v>21.33970013842667</v>
       </c>
       <c r="O3" t="n">
-        <v>4.620777712748248</v>
+        <v>4.619491328969746</v>
       </c>
       <c r="P3" t="n">
-        <v>377.2174766197738</v>
+        <v>377.2779189208537</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19855,28 +19991,28 @@
         <v>0.0502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0413014569878038</v>
+        <v>0.03155579851765277</v>
       </c>
       <c r="J4" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K4" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004046375514649481</v>
+        <v>0.002367063052111651</v>
       </c>
       <c r="M4" t="n">
-        <v>4.025841475653881</v>
+        <v>4.047254220376304</v>
       </c>
       <c r="N4" t="n">
-        <v>25.80287682892925</v>
+        <v>25.99866485610795</v>
       </c>
       <c r="O4" t="n">
-        <v>5.079653219357524</v>
+        <v>5.098888590281999</v>
       </c>
       <c r="P4" t="n">
-        <v>380.1595901778207</v>
+        <v>380.2580227279751</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19933,28 +20069,28 @@
         <v>0.0301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1972862593068522</v>
+        <v>0.1852534608452913</v>
       </c>
       <c r="J5" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K5" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03731260618119636</v>
+        <v>0.03322670528640326</v>
       </c>
       <c r="M5" t="n">
-        <v>5.899086042088991</v>
+        <v>5.930234512330358</v>
       </c>
       <c r="N5" t="n">
-        <v>61.7145872918078</v>
+        <v>61.85883981351245</v>
       </c>
       <c r="O5" t="n">
-        <v>7.855863242942038</v>
+        <v>7.865039085313718</v>
       </c>
       <c r="P5" t="n">
-        <v>391.4540673765654</v>
+        <v>391.5755968137075</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19992,7 +20128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F543"/>
+  <dimension ref="A1:F547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37363,6 +37499,134 @@
         </is>
       </c>
     </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>-34.950516046011714,173.61978395408758</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>-34.95122050327247,173.61983488181733</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>-34.95187386774941,173.62013953449423</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-34.95233341203061,173.6208187374453</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>-34.950516046011714,173.61978395408758</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>-34.951219415017604,173.6198443177419</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>-34.95187121849779,173.6201448839034</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-34.95233805085849,173.62081217134292</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>-34.950515544984164,173.61977807156865</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>-34.951219602647804,173.61984269085835</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>-34.95186726785897,173.62015286109184</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-34.952322725109354,173.62083386441248</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>-34.950515544984164,173.61977807156865</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>-34.95121936498288,173.6198447515775</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>-34.951864943953545,173.62015755355526</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-34.952316089822155,173.6208432564286</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
